--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137053407</v>
       </c>
       <c r="B2" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137053407</v>
       </c>
       <c r="B2" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -713,11 +713,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hundmossen, Hundmossen, Upl</t>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137053407</v>
+        <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>58137</v>
+        <v>92822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100090</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hundmossen, Hundmossen, Upl</t>
+          <t>Mörtsjön V, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625700</v>
+        <v>625646</v>
       </c>
       <c r="R2" t="n">
-        <v>6650907</v>
+        <v>6650966</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,24 +775,378 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Söderström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Söderström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137288408</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137288409</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mörtsjön V, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>625650</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6650967</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137288409</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137053407</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58137</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hundmossen, Hundmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>625700</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6650907</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Söderström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Söderström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137053407</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137288416</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörtsjön V, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>625654</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6650708</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137288416</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137053407</v>
       </c>
       <c r="B4" t="n">
-        <v>58137</v>
+        <v>58147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137288416</v>
       </c>
       <c r="B5" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137053407</v>
       </c>
       <c r="B4" t="n">
-        <v>58147</v>
+        <v>58148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137053407</v>
       </c>
       <c r="B4" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32103-2026 artfynd.xlsx
+++ b/artfynd/A 32103-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137288408</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137288409</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137053407</v>
       </c>
       <c r="B4" t="n">
-        <v>58149</v>
+        <v>58152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
